--- a/Excel/JulianGoldieSEO.xlsx
+++ b/Excel/JulianGoldieSEO.xlsx
@@ -463,25 +463,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d7IxBkUrVbI</t>
+          <t>DS37JuZ2IP8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Google MCP Agents are INSANE 🤯</t>
+          <t>OpenCode + AntiGravity is INSANE!  🤯</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>455953</v>
+        <v>24933</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0:00:59</t>
+          <t>0:08:12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,25 +493,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LB4PIqXzv48</t>
+          <t>ul7zuyATDqE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NEW 1-Click Google AI Agents are INSANE! 🤯</t>
+          <t>OpenCode is INSANE!</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>345869</v>
+        <v>14511</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0:00:44</t>
+          <t>0:11:38</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,25 +523,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4x-aAIHIUxM</t>
+          <t>D2fFhra4gos</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro + Veo 3 is INSANE!</t>
+          <t>DeepSeek V4 Update is INSANE!</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>210039</v>
+        <v>13104</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0:00:57</t>
+          <t>0:07:47</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -553,25 +553,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6xoINKGaB0c</t>
+          <t>Y5F-4YlYmOM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro MCP Servers: Automate ANYTHING!</t>
+          <t>OpenCode is INSANE!</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>157400</v>
+        <v>12987</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0:01:00</t>
+          <t>0:00:38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,25 +583,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WRJZT0DTGjY</t>
+          <t>z8K7Ur-Exmo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Google Veo 3 is WILD!</t>
+          <t>DeepSeek V4 Update is INSANE!</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>127181</v>
+        <v>12512</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0:16:06</t>
+          <t>0:00:32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -613,25 +613,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Us3ao0vPIG8</t>
+          <t>HljFkgXnf7M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEW 1-Click Google AI Agents are INSANE! 🤯</t>
+          <t>NEW DeepSeek V4 Leaks Are INSANE!</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>119524</v>
+        <v>12365</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0:16:17</t>
+          <t>0:08:16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -643,25 +643,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>daYrZOlX0rc</t>
+          <t>g2sQmiGfBEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEW Gemini 3.0: Leaks + Rumours!</t>
+          <t>OpenCode + Antigravity is INSANE (FREE!) 🤯</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>118780</v>
+        <v>11772</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0:00:34</t>
+          <t>0:07:16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -673,25 +673,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OaS_6QKJnww</t>
+          <t>NZzEmSPi0ms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Google Stitch: Build Apps in 1 Click (FREE)! 🤯</t>
+          <t>Build Anything with OpenCode, Here is How (FREE!)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>115127</v>
+        <v>11391</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0:00:57</t>
+          <t>0:09:06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -703,25 +703,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>moyn-0EkotY</t>
+          <t>3f3UD0LWk-s</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Google Veo 3 is INSANE 🤯</t>
+          <t>OpenCode + AntiGravity is INSANE! 🤯</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>92371</v>
+        <v>10834</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0:00:59</t>
+          <t>0:00:31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -733,25 +733,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vF4KjwdxW8w</t>
+          <t>c_aTbvmO2ko</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New Google NotebookLM Update Is INSANE (FREE!) 🤯</t>
+          <t>KIMI 2.6 + OpenCode Is INSANE! 🤯</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84752</v>
+        <v>10525</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0:15:38</t>
+          <t>0:08:37</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
